--- a/human_resources_forms/026_staff_longevity_and_attrition_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/026_staff_longevity_and_attrition_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What Is The Purpose Of This Survey</t>
+          <t>What is the purpose of this survey?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Please answer this questions honestly</t>
+          <t>Please answer this question honestly</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How Long Have You Been With This Company</t>
+          <t>How long have you been with this company?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Years</t>
+          <t>In years</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Why Do You Leave Your Job</t>
+          <t>What are the main reasons you would leave your job?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -592,7 +592,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How Satisfied Are You With Your Job</t>
+          <t>How satisfied are you with your job?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How Often Do You Have Positive Interactions With Your Manager</t>
+          <t>How often do you have positive interactions with your manager?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Any Additional Feedback?</t>
+          <t>Do you have any additional feedback?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>manager_performance</t>
+          <t>org_change</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manager Performance</t>
+          <t>How often do you see changes in the organization?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -688,17 +688,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_satisfaction_2</t>
+          <t>org_change_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How Satisfied Are You With Your Job</t>
+          <t>What kind of changes have you seen in the organization?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -716,19 +716,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>team_survey</t>
+          <t>org_change_pos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How Often Do You Have Positive Interactions With Your Team</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Scale of 1-5</t>
-        </is>
-      </c>
+          <t>How often do you see positive changes in the organization?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -743,19 +739,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>org_change</t>
+          <t>org_change_neg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Scale of 1-5</t>
-        </is>
-      </c>
+          <t>How often do you see negative changes in the organization?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -765,17 +757,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>org_change_2</t>
+          <t>org_change_pol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company policies?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -788,17 +780,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>org_change_3</t>
+          <t>org_change_pro</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company procedures?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -811,17 +803,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>org_change_4</t>
+          <t>org_change_cul</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company culture?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -839,12 +831,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>org_change_5</t>
+          <t>org_change_vis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company vision?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -862,12 +854,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>org_change_6</t>
+          <t>org_change_mis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company mission?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -885,12 +877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>org_change_7</t>
+          <t>org_change_val</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company values?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +900,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>org_change_8</t>
+          <t>org_change_lea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company leadership?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -931,154 +923,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>org_change_9</t>
+          <t>org_change_com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How Often Do You See Changes In The Organization</t>
+          <t>How often do you see changes in company communication?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>org_change_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>org_change_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>org_change_12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>org_change_13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>org_change_14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>org_change_15</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How Often Do You See Changes In The Organization</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1095,10 +949,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1281,12 +1135,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1152,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1315,512 +1169,512 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>manager_survey_choices</t>
+          <t>org_change_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>manager_survey_choices</t>
+          <t>org_change_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>manager_performance_choices</t>
+          <t>org_change_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>manager_performance_choices</t>
+          <t>org_change_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manager_performance_choices</t>
+          <t>org_change_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>manager_performance_choices</t>
+          <t>org_change_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>org_change_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>org_change_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>org_change_pos_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>org_change_pos_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>org_change_pos_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>org_change_neg_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>org_change_neg_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>org_change_neg_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>org_change_pol_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>org_change_pol_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>org_change_choices</t>
+          <t>org_change_pol_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>org_change_choices</t>
+          <t>org_change_pro_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>org_change_choices</t>
+          <t>org_change_pro_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>org_change_choices</t>
+          <t>org_change_pro_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>org_change_choices</t>
+          <t>org_change_cul_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>org_change_2_choices</t>
+          <t>org_change_cul_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>org_change_2_choices</t>
+          <t>org_change_cul_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>org_change_2_choices</t>
+          <t>org_change_vis_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>org_change_3_choices</t>
+          <t>org_change_vis_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>org_change_3_choices</t>
+          <t>org_change_vis_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>org_change_3_choices</t>
+          <t>org_change_mis_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>org_change_3_choices</t>
+          <t>org_change_mis_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>org_change_3_choices</t>
+          <t>org_change_mis_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>org_change_4_choices</t>
+          <t>org_change_val_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1837,7 +1691,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>org_change_4_choices</t>
+          <t>org_change_val_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1854,7 +1708,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>org_change_4_choices</t>
+          <t>org_change_val_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1871,731 +1725,102 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>org_change_5_choices</t>
+          <t>org_change_lea_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>org_change_5_choices</t>
+          <t>org_change_lea_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>org_change_5_choices</t>
+          <t>org_change_lea_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>org_change_5_choices</t>
+          <t>org_change_com_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>org_change_5_choices</t>
+          <t>org_change_com_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>org_change_6_choices</t>
+          <t>org_change_com_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>org_change_6_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>org_change_6_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
           <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>org_change_7_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>org_change_7_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>org_change_7_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>org_change_8_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>org_change_8_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>org_change_8_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>org_change_8_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>org_change_8_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Yearly</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>org_change_9_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>org_change_9_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>org_change_9_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>org_change_10_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>org_change_10_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>org_change_10_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>org_change_10_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>org_change_10_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Yearly</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>org_change_11_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>org_change_11_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>org_change_11_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>org_change_12_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>org_change_12_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>org_change_12_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>org_change_12_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>org_change_12_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Yearly</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>org_change_13_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>org_change_13_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>org_change_13_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>org_change_14_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>org_change_14_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>org_change_14_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>org_change_15_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>org_change_15_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>org_change_15_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>org_change_15_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>org_change_15_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Yearly</t>
         </is>
       </c>
     </row>
